--- a/artfynd/A 39172-2022 artfynd.xlsx
+++ b/artfynd/A 39172-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39172-2022 artfynd.xlsx
+++ b/artfynd/A 39172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104047729</v>
+        <v>104047685</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554131.5704110946</v>
+        <v>554868</v>
       </c>
       <c r="R2" t="n">
-        <v>7059997.972699852</v>
+        <v>7059815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,17 +778,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -811,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104047733</v>
+        <v>104047698</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554468.8357475931</v>
+        <v>554129</v>
       </c>
       <c r="R3" t="n">
-        <v>7059963.342583247</v>
+        <v>7059966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -947,15 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104047698</v>
+        <v>104047732</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,26 +948,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -996,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554129.0050523889</v>
+        <v>554326</v>
       </c>
       <c r="R4" t="n">
-        <v>7059965.949759084</v>
+        <v>7060144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1031,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1041,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,17 +1040,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1083,42 +1068,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104047703</v>
+        <v>104047681</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,10 +1112,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554334.7613648062</v>
+        <v>554939</v>
       </c>
       <c r="R5" t="n">
-        <v>7060130.701037544</v>
+        <v>7059898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1167,7 +1147,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1177,7 +1157,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,6 +1168,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1204,37 +1199,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104047694</v>
+        <v>104047696</v>
       </c>
       <c r="B6" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1253,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554202.2198851865</v>
+        <v>554175</v>
       </c>
       <c r="R6" t="n">
-        <v>7059845.946213342</v>
+        <v>7059841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1288,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1298,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,6 +1299,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>På flera granlågor # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1325,42 +1330,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104047702</v>
+        <v>104047697</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554151.5210234076</v>
+        <v>554159</v>
       </c>
       <c r="R7" t="n">
-        <v>7060079.592738369</v>
+        <v>7059833</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,6 +1430,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1446,15 +1461,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104047713</v>
+        <v>104047704</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,31 +1472,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1495,10 +1505,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554753.7490037414</v>
+        <v>554413</v>
       </c>
       <c r="R8" t="n">
-        <v>7059793.256688285</v>
+        <v>7060010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,7 +1540,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1540,7 +1550,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,17 +1564,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1582,42 +1592,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104047727</v>
+        <v>104047701</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>1179</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1631,10 +1636,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554297.8402685525</v>
+        <v>554131</v>
       </c>
       <c r="R9" t="n">
-        <v>7059716.551788744</v>
+        <v>7059998</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1666,7 +1671,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1676,7 +1681,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,17 +1695,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>På död gren av döende sälg där grenen låg precis ovanför mossan i fuktig sluttning. # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1718,42 +1723,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104047701</v>
+        <v>104047684</v>
       </c>
       <c r="B10" t="n">
-        <v>89967</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554131.5704110946</v>
+        <v>554939</v>
       </c>
       <c r="R10" t="n">
-        <v>7059997.972699852</v>
+        <v>7059898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,17 +1826,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På död gren av döende sälg där grenen låg precis ovanför mossan i fuktig sluttning. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1854,15 +1854,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104047696</v>
+        <v>105226761</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,46 +1865,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554175.6256095261</v>
+        <v>554150</v>
       </c>
       <c r="R11" t="n">
-        <v>7059840.604871987</v>
+        <v>7059651</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1933,22 +1920,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,46 +1936,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>På flera granlågor # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104047706</v>
+        <v>105226883</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2006,46 +1963,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554699.8725635095</v>
+        <v>554179</v>
       </c>
       <c r="R12" t="n">
-        <v>7059719.47802787</v>
+        <v>7059662</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2069,22 +2018,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2095,46 +2034,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104047730</v>
+        <v>105228616</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2142,46 +2061,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554170.3727045077</v>
+        <v>554240</v>
       </c>
       <c r="R13" t="n">
-        <v>7060095.460305991</v>
+        <v>7059661</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2205,22 +2116,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:34</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2231,73 +2132,53 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104047697</v>
+        <v>104047686</v>
       </c>
       <c r="B14" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2311,10 +2192,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554158.3989453822</v>
+        <v>554825</v>
       </c>
       <c r="R14" t="n">
-        <v>7059833.647369988</v>
+        <v>7059793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2346,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2356,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,17 +2251,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2398,15 +2279,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104047714</v>
+        <v>104047687</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2414,26 +2290,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2447,10 +2323,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554718.5624968933</v>
+        <v>554571</v>
       </c>
       <c r="R15" t="n">
-        <v>7059744.675888207</v>
+        <v>7059676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2482,7 +2358,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2492,7 +2368,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,17 +2382,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2534,42 +2410,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104047734</v>
+        <v>104047695</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2583,10 +2454,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554591.312342982</v>
+        <v>554179</v>
       </c>
       <c r="R16" t="n">
-        <v>7060004.983184493</v>
+        <v>7059840</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2618,7 +2489,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2628,7 +2499,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2642,17 +2513,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2670,62 +2541,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104047695</v>
+        <v>105226844</v>
       </c>
       <c r="B17" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1503</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554179.6425075377</v>
+        <v>554180</v>
       </c>
       <c r="R17" t="n">
-        <v>7059839.785301066</v>
+        <v>7059658</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2749,22 +2607,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2775,46 +2623,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104047720</v>
+        <v>104047694</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2822,31 +2650,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2855,10 +2683,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554702.9057483793</v>
+        <v>554202</v>
       </c>
       <c r="R18" t="n">
-        <v>7059492.539555158</v>
+        <v>7059846</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2890,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2900,7 +2728,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2911,21 +2739,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2942,15 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104047704</v>
+        <v>104047702</v>
       </c>
       <c r="B19" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2958,26 +2766,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2991,10 +2799,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554413.3309984311</v>
+        <v>554151</v>
       </c>
       <c r="R19" t="n">
-        <v>7060009.912105353</v>
+        <v>7060079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3026,7 +2834,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3036,7 +2844,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,21 +2855,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3078,15 +2871,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104047728</v>
+        <v>104047703</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3094,31 +2882,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3127,10 +2915,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554168.4886859619</v>
+        <v>554335</v>
       </c>
       <c r="R20" t="n">
-        <v>7059841.815208253</v>
+        <v>7060131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3162,7 +2950,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3172,7 +2960,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3183,21 +2971,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3214,62 +2987,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104047732</v>
+        <v>105226544</v>
       </c>
       <c r="B21" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>554325.6484403363</v>
+        <v>554168</v>
       </c>
       <c r="R21" t="n">
-        <v>7060143.424404758</v>
+        <v>7059538</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3293,22 +3053,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3319,93 +3069,65 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104047731</v>
+        <v>105226739</v>
       </c>
       <c r="B22" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554190.5164368353</v>
+        <v>554134</v>
       </c>
       <c r="R22" t="n">
-        <v>7060087.810761812</v>
+        <v>7059627</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3429,22 +3151,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3455,68 +3167,48 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105226844</v>
+        <v>105226948</v>
       </c>
       <c r="B23" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3527,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554179.6472303394</v>
+        <v>554133</v>
       </c>
       <c r="R23" t="n">
-        <v>7059657.668952459</v>
+        <v>7059770</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3560,19 +3252,9 @@
           <t>2022-12-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-12-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3599,37 +3281,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>105226896</v>
+        <v>105226999</v>
       </c>
       <c r="B24" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3640,10 +3317,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554188.1790017824</v>
+        <v>554107</v>
       </c>
       <c r="R24" t="n">
-        <v>7059704.899801441</v>
+        <v>7060007</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3673,19 +3350,9 @@
           <t>2022-12-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-12-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3712,32 +3379,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>105227920</v>
+        <v>105228183</v>
       </c>
       <c r="B25" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3749,14 +3411,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Äxingsberget, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554336.5016055009</v>
+        <v>554196</v>
       </c>
       <c r="R25" t="n">
-        <v>7060132.951592109</v>
+        <v>7059856</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3786,19 +3448,9 @@
           <t>2022-12-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-12-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3825,37 +3477,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>105227009</v>
+        <v>105228518</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3866,10 +3513,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554093.1745108622</v>
+        <v>554189</v>
       </c>
       <c r="R26" t="n">
-        <v>7060006.643207183</v>
+        <v>7059724</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3899,19 +3546,9 @@
           <t>2022-12-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-12-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3938,54 +3575,57 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>105226739</v>
+        <v>104047727</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>554134.3716009881</v>
+        <v>554298</v>
       </c>
       <c r="R27" t="n">
-        <v>7059626.244225571</v>
+        <v>7059716</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4009,22 +3649,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4035,31 +3675,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>105228815</v>
+        <v>104047706</v>
       </c>
       <c r="B28" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4067,38 +3717,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>554239.6456263677</v>
+        <v>554700</v>
       </c>
       <c r="R28" t="n">
-        <v>7059660.473559706</v>
+        <v>7059719</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4122,22 +3780,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4148,70 +3806,88 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105226898</v>
+        <v>104047707</v>
       </c>
       <c r="B29" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>554187.1832418398</v>
+        <v>554990</v>
       </c>
       <c r="R29" t="n">
-        <v>7059711.101440185</v>
+        <v>7059799</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4235,22 +3911,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4261,31 +3937,41 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105226948</v>
+        <v>104047708</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4293,38 +3979,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>554132.3549874128</v>
+        <v>555084</v>
       </c>
       <c r="R30" t="n">
-        <v>7059770.128335833</v>
+        <v>7059881</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4348,22 +4042,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4374,31 +4068,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105227705</v>
+        <v>104047709</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4423,21 +4127,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>554225.3774264655</v>
+        <v>555118</v>
       </c>
       <c r="R31" t="n">
-        <v>7060259.396998069</v>
+        <v>7059976</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4461,22 +4173,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4487,31 +4199,41 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105227555</v>
+        <v>104047711</v>
       </c>
       <c r="B32" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4519,38 +4241,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>554053.6763167785</v>
+        <v>554954</v>
       </c>
       <c r="R32" t="n">
-        <v>7060236.029418521</v>
+        <v>7060050</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4574,22 +4304,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4600,31 +4330,41 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105228183</v>
+        <v>104047712</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4632,38 +4372,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>554196.2647481549</v>
+        <v>554902</v>
       </c>
       <c r="R33" t="n">
-        <v>7059856.060170767</v>
+        <v>7059839</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4687,22 +4435,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4713,70 +4461,88 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>vanlig vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Betula pendula var. pendula</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Betula pendula var. pendula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105226849</v>
+        <v>104047713</v>
       </c>
       <c r="B34" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>554178.681885635</v>
+        <v>554754</v>
       </c>
       <c r="R34" t="n">
-        <v>7059662.094413185</v>
+        <v>7059793</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4800,22 +4566,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4826,31 +4592,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105226761</v>
+        <v>104047714</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4858,38 +4634,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>554150.8432354623</v>
+        <v>554718</v>
       </c>
       <c r="R35" t="n">
-        <v>7059651.401333001</v>
+        <v>7059745</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4913,22 +4697,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4939,31 +4723,41 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105228616</v>
+        <v>104047715</v>
       </c>
       <c r="B36" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4971,38 +4765,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>554239.6456263677</v>
+        <v>554940</v>
       </c>
       <c r="R36" t="n">
-        <v>7059660.473559706</v>
+        <v>7059718</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5026,22 +4828,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5052,31 +4854,41 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105226883</v>
+        <v>104047716</v>
       </c>
       <c r="B37" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5084,38 +4896,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>554178.681885635</v>
+        <v>554843</v>
       </c>
       <c r="R37" t="n">
-        <v>7059662.094413185</v>
+        <v>7059664</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5139,22 +4959,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5165,31 +4985,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>vanlig vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula pendula var. pendula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Betula pendula var. pendula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105226999</v>
+        <v>104047720</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5197,38 +5027,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>554106.5127820438</v>
+        <v>554703</v>
       </c>
       <c r="R38" t="n">
-        <v>7060006.871268683</v>
+        <v>7059493</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5252,22 +5090,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,31 +5116,41 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105228128</v>
+        <v>104047722</v>
       </c>
       <c r="B39" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5327,21 +5175,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>554301.9598373107</v>
+        <v>554334</v>
       </c>
       <c r="R39" t="n">
-        <v>7059891.184964792</v>
+        <v>7059653</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5365,22 +5221,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5391,31 +5247,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105227711</v>
+        <v>104047723</v>
       </c>
       <c r="B40" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5423,38 +5289,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>554223.9600005152</v>
+        <v>554346</v>
       </c>
       <c r="R40" t="n">
-        <v>7060264.257967762</v>
+        <v>7059651</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5478,22 +5352,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5504,31 +5378,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105228124</v>
+        <v>104047728</v>
       </c>
       <c r="B41" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5536,38 +5420,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>554305.908120035</v>
+        <v>554169</v>
       </c>
       <c r="R41" t="n">
-        <v>7059894.361893782</v>
+        <v>7059842</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5591,22 +5483,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5617,31 +5509,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105226785</v>
+        <v>104047729</v>
       </c>
       <c r="B42" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5666,21 +5568,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>554150.9268236872</v>
+        <v>554131</v>
       </c>
       <c r="R42" t="n">
-        <v>7059646.516560988</v>
+        <v>7059998</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5704,22 +5614,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5730,31 +5640,41 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105228518</v>
+        <v>104047730</v>
       </c>
       <c r="B43" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5762,38 +5682,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+          <t>Väster-Äxingen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>554188.7413197273</v>
+        <v>554170</v>
       </c>
       <c r="R43" t="n">
-        <v>7059724.009654745</v>
+        <v>7060096</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5817,22 +5745,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-12-18</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5843,31 +5771,41 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>104047684</v>
+        <v>104047731</v>
       </c>
       <c r="B44" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5875,26 +5813,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5908,10 +5846,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>554939.6212122502</v>
+        <v>554190</v>
       </c>
       <c r="R44" t="n">
-        <v>7059898.194859669</v>
+        <v>7060088</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5943,7 +5881,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5953,7 +5891,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5967,17 +5905,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5995,15 +5933,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104047707</v>
+        <v>104047733</v>
       </c>
       <c r="B45" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6030,7 +5963,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6044,10 +5977,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>554989.8215580435</v>
+        <v>554469</v>
       </c>
       <c r="R45" t="n">
-        <v>7059799.127110215</v>
+        <v>7059964</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6079,7 +6012,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6089,7 +6022,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6131,15 +6064,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104047712</v>
+        <v>104047734</v>
       </c>
       <c r="B46" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6166,7 +6094,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6180,10 +6108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>554902.4004646906</v>
+        <v>554591</v>
       </c>
       <c r="R46" t="n">
-        <v>7059838.917899939</v>
+        <v>7060005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6215,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6225,7 +6153,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6239,17 +6167,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>vanlig vårtbjörk</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Betula pendula var. pendula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Betula pendula var. pendula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6267,15 +6195,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104047716</v>
+        <v>105226527</v>
       </c>
       <c r="B47" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6300,29 +6223,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>554843.605588217</v>
+        <v>554163</v>
       </c>
       <c r="R47" t="n">
-        <v>7059664.220142454</v>
+        <v>7059542</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6346,22 +6261,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6375,43 +6280,43 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>vanlig vårtbjörk</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Betula pendula var. pendula</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Betula pendula var. pendula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104047681</v>
+        <v>105226785</v>
       </c>
       <c r="B48" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6419,46 +6324,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>554939.6212122502</v>
+        <v>554151</v>
       </c>
       <c r="R48" t="n">
-        <v>7059898.194859669</v>
+        <v>7059647</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6482,22 +6379,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:44</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6508,93 +6395,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>104047686</v>
+        <v>105226896</v>
       </c>
       <c r="B49" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>554824.9143826535</v>
+        <v>554189</v>
       </c>
       <c r="R49" t="n">
-        <v>7059793.156346929</v>
+        <v>7059705</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6618,22 +6477,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6644,46 +6493,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>104047709</v>
+        <v>105227009</v>
       </c>
       <c r="B50" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6708,29 +6537,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555117.5132184264</v>
+        <v>554094</v>
       </c>
       <c r="R50" t="n">
-        <v>7059975.464141178</v>
+        <v>7060007</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6754,22 +6575,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6780,46 +6591,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>104047715</v>
+        <v>105227705</v>
       </c>
       <c r="B51" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6844,29 +6635,21 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>554939.6466027095</v>
+        <v>554225</v>
       </c>
       <c r="R51" t="n">
-        <v>7059717.413115614</v>
+        <v>7060259</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6890,22 +6673,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6916,46 +6689,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104047685</v>
+        <v>105228128</v>
       </c>
       <c r="B52" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6963,46 +6716,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>554868.5563993073</v>
+        <v>554302</v>
       </c>
       <c r="R52" t="n">
-        <v>7059815.677721276</v>
+        <v>7059891</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7026,22 +6771,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:36</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7052,46 +6787,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104047711</v>
+        <v>104047737</v>
       </c>
       <c r="B53" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7099,31 +6814,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7132,10 +6847,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>554953.4502709296</v>
+        <v>554941</v>
       </c>
       <c r="R53" t="n">
-        <v>7060049.449098795</v>
+        <v>7059873</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7167,7 +6882,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7177,7 +6892,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7188,21 +6903,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7219,62 +6919,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104047708</v>
+        <v>105226849</v>
       </c>
       <c r="B54" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Väster-Äxingen, Ång</t>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555083.5750951129</v>
+        <v>554179</v>
       </c>
       <c r="R54" t="n">
-        <v>7059881.154054588</v>
+        <v>7059662</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7298,22 +6985,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7324,34 +7001,607 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>105226898</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>554187</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7059711</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>105227555</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>554053</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7060236</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>105227711</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>554224</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7060265</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>105227920</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Äxingsberget, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>554337</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7060133</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>105228124</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>554306</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7059894</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>105228815</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Väster-Äxingen, Ramsele, Ång, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>554240</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7059661</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39172-2022 artfynd.xlsx
+++ b/artfynd/A 39172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047732</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,6 +1216,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047681</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1327,6 +1352,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047696</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1458,6 +1488,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047697</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1589,6 +1624,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047704</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1720,6 +1760,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1851,6 +1896,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047684</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1949,6 +1999,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226761</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2047,6 +2102,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226883</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2145,6 +2205,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228616</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2276,6 +2341,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047686</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2407,6 +2477,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047687</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2538,6 +2613,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047695</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2636,6 +2716,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226844</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2752,6 +2837,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047694</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2868,6 +2958,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047702</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2984,6 +3079,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3082,6 +3182,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226544</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3180,6 +3285,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226739</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3278,6 +3388,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226948</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3376,6 +3491,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226999</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3474,6 +3594,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228183</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3572,6 +3697,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228518</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3703,6 +3833,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047727</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3834,6 +3969,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047706</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3965,6 +4105,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047707</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4096,6 +4241,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047708</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4227,6 +4377,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047709</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4358,6 +4513,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047711</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4489,6 +4649,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047712</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4620,6 +4785,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047713</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4751,6 +4921,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047714</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4882,6 +5057,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047715</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5013,6 +5193,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047716</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5144,6 +5329,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047720</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5275,6 +5465,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047722</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5406,6 +5601,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047723</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5537,6 +5737,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047728</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5668,6 +5873,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047729</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5799,6 +6009,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047730</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5930,6 +6145,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047731</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6061,6 +6281,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047733</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6192,6 +6417,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047734</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6310,6 +6540,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226527</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6408,6 +6643,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226785</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6506,6 +6746,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226896</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6604,6 +6849,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227009</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6702,6 +6952,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227705</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6800,6 +7055,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228128</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6916,6 +7176,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104047737</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7014,6 +7279,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226849</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7112,6 +7382,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105226898</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7210,6 +7485,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227555</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7308,6 +7588,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227711</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7406,6 +7691,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105227920</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7504,6 +7794,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228124</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7602,8 +7897,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105228815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>